--- a/Docs/params_catalog/SPOD_PARAMS_CATALOG.xlsx
+++ b/Docs/params_catalog/SPOD_PARAMS_CATALOG.xlsx
@@ -32386,7 +32386,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 14:06:05</t>
+          <t>2026-08-06 14:08:26</t>
         </is>
       </c>
     </row>
@@ -32398,7 +32398,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>/workspace/IN/SPOD_UPLOAD</t>
+          <t>IN/SPOD_UPLOAD</t>
         </is>
       </c>
     </row>
